--- a/data/base/Backlog_32.xlsx
+++ b/data/base/Backlog_32.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BAC4DB-91CC-4E52-A67A-2FC38571DB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C27970-AFB9-4025-9ABB-14B24DD04E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7B6DCF3-E10E-448D-89E5-FD6D35B80F1D}"/>
   </bookViews>
@@ -456,7 +456,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -586,19 +586,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -644,7 +631,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -655,31 +642,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1058,52 +1033,51 @@
   <dimension ref="A1:K66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="5.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1111,34 +1085,34 @@
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="7">
-        <v>32</v>
-      </c>
-      <c r="E2" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F2" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="C2" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="4">
+        <v>32</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G2" s="4">
         <v>22708</v>
       </c>
-      <c r="H2" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I2" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="H2" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I2" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1146,34 +1120,34 @@
       <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="7">
-        <v>32</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F3" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="C3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="4">
+        <v>32</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G3" s="4">
         <v>21876</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="7">
         <v>46204</v>
       </c>
-      <c r="I3" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="I3" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1181,34 +1155,34 @@
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="7">
-        <v>32</v>
-      </c>
-      <c r="E4" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F4" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="C4" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="4">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G4" s="4">
         <v>22577</v>
       </c>
-      <c r="H4" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I4" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="H4" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1216,34 +1190,34 @@
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="7">
-        <v>32</v>
-      </c>
-      <c r="E5" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F5" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="C5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="4">
+        <v>32</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G5" s="4">
         <v>20486</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="7">
         <v>46204</v>
       </c>
-      <c r="I5" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="I5" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1251,34 +1225,34 @@
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="7">
-        <v>32</v>
-      </c>
-      <c r="E6" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F6" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="C6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="4">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G6" s="4">
         <v>22080</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="7">
         <v>46204</v>
       </c>
-      <c r="I6" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="I6" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1286,34 +1260,34 @@
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="7">
-        <v>32</v>
-      </c>
-      <c r="E7" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F7" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="C7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="4">
+        <v>32</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G7" s="4">
         <v>22383</v>
       </c>
-      <c r="H7" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I7" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="H7" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I7" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1321,34 +1295,34 @@
       <c r="A8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="7">
-        <v>32</v>
-      </c>
-      <c r="E8" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F8" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="C8" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="4">
+        <v>32</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G8" s="4">
         <v>22555</v>
       </c>
-      <c r="H8" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I8" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="H8" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I8" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1356,34 +1330,34 @@
       <c r="A9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="7">
-        <v>32</v>
-      </c>
-      <c r="E9" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F9" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G9" s="7">
+      <c r="C9" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="4">
+        <v>32</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G9" s="4">
         <v>22647</v>
       </c>
-      <c r="H9" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I9" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="7" t="s">
+      <c r="H9" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1391,34 +1365,34 @@
       <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="7">
-        <v>32</v>
-      </c>
-      <c r="E10" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F10" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="C10" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32</v>
+      </c>
+      <c r="E10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G10" s="4">
         <v>22803</v>
       </c>
-      <c r="H10" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I10" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="7" t="s">
+      <c r="H10" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1426,34 +1400,34 @@
       <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="7">
-        <v>32</v>
-      </c>
-      <c r="E11" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F11" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="C11" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="4">
+        <v>32</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G11" s="4">
         <v>22140</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="7">
         <v>46204</v>
       </c>
-      <c r="I11" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="7" t="s">
+      <c r="I11" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1461,34 +1435,34 @@
       <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="7">
-        <v>32</v>
-      </c>
-      <c r="E12" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F12" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="C12" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="4">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G12" s="4">
         <v>22583</v>
       </c>
-      <c r="H12" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I12" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="H12" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1496,34 +1470,34 @@
       <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="7">
-        <v>32</v>
-      </c>
-      <c r="E13" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F13" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G13" s="7">
+      <c r="C13" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="4">
+        <v>32</v>
+      </c>
+      <c r="E13" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G13" s="4">
         <v>22187</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <v>46204</v>
       </c>
-      <c r="I13" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="7" t="s">
+      <c r="I13" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1531,34 +1505,34 @@
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="7">
-        <v>32</v>
-      </c>
-      <c r="E14" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F14" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G14" s="7">
+      <c r="C14" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="4">
+        <v>32</v>
+      </c>
+      <c r="E14" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G14" s="4">
         <v>22660</v>
       </c>
-      <c r="H14" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I14" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="7" t="s">
+      <c r="H14" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I14" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1566,34 +1540,34 @@
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="7">
-        <v>32</v>
-      </c>
-      <c r="E15" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F15" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G15" s="7">
+      <c r="C15" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="4">
+        <v>32</v>
+      </c>
+      <c r="E15" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G15" s="4">
         <v>22993</v>
       </c>
-      <c r="H15" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I15" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="7" t="s">
+      <c r="H15" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I15" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1601,34 +1575,34 @@
       <c r="A16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="7">
-        <v>32</v>
-      </c>
-      <c r="E16" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F16" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G16" s="7">
+      <c r="C16" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="4">
+        <v>32</v>
+      </c>
+      <c r="E16" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G16" s="4">
         <v>23042</v>
       </c>
-      <c r="H16" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I16" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="7" t="s">
+      <c r="H16" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I16" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1636,34 +1610,34 @@
       <c r="A17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="7">
-        <v>32</v>
-      </c>
-      <c r="E17" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F17" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G17" s="7">
+      <c r="C17" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="4">
+        <v>32</v>
+      </c>
+      <c r="E17" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G17" s="4">
         <v>22311</v>
       </c>
-      <c r="H17" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I17" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K17" s="7" t="s">
+      <c r="H17" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I17" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1671,34 +1645,34 @@
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="7">
-        <v>32</v>
-      </c>
-      <c r="E18" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F18" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G18" s="7">
+      <c r="C18" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="4">
+        <v>32</v>
+      </c>
+      <c r="E18" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G18" s="4">
         <v>22483</v>
       </c>
-      <c r="H18" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I18" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" s="7" t="s">
+      <c r="H18" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I18" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1706,34 +1680,34 @@
       <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="7">
-        <v>32</v>
-      </c>
-      <c r="E19" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F19" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="C19" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="4">
+        <v>32</v>
+      </c>
+      <c r="E19" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F19" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G19" s="4">
         <v>22487</v>
       </c>
-      <c r="H19" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I19" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="7" t="s">
+      <c r="H19" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I19" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1741,34 +1715,34 @@
       <c r="A20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="7">
-        <v>32</v>
-      </c>
-      <c r="E20" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F20" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G20" s="7">
+      <c r="C20" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="4">
+        <v>32</v>
+      </c>
+      <c r="E20" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G20" s="4">
         <v>22605</v>
       </c>
-      <c r="H20" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I20" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="7" t="s">
+      <c r="H20" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I20" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1776,34 +1750,34 @@
       <c r="A21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="7">
-        <v>32</v>
-      </c>
-      <c r="E21" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F21" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G21" s="7">
+      <c r="C21" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="4">
+        <v>32</v>
+      </c>
+      <c r="E21" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G21" s="4">
         <v>22680</v>
       </c>
-      <c r="H21" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I21" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="7" t="s">
+      <c r="H21" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I21" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1811,34 +1785,34 @@
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="7">
-        <v>32</v>
-      </c>
-      <c r="E22" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F22" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G22" s="7">
+      <c r="C22" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="4">
+        <v>32</v>
+      </c>
+      <c r="E22" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G22" s="4">
         <v>22718</v>
       </c>
-      <c r="H22" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I22" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" s="7" t="s">
+      <c r="H22" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I22" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1846,34 +1820,34 @@
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="7">
-        <v>32</v>
-      </c>
-      <c r="E23" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F23" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G23" s="7">
+      <c r="C23" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="4">
+        <v>32</v>
+      </c>
+      <c r="E23" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G23" s="4">
         <v>22720</v>
       </c>
-      <c r="H23" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I23" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="7" t="s">
+      <c r="H23" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I23" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1881,34 +1855,34 @@
       <c r="A24" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="7">
-        <v>32</v>
-      </c>
-      <c r="E24" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F24" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G24" s="7">
+      <c r="C24" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="4">
+        <v>32</v>
+      </c>
+      <c r="E24" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F24" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G24" s="4">
         <v>22725</v>
       </c>
-      <c r="H24" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I24" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" s="7" t="s">
+      <c r="H24" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I24" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1916,34 +1890,34 @@
       <c r="A25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="7">
-        <v>32</v>
-      </c>
-      <c r="E25" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F25" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G25" s="7">
+      <c r="C25" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="4">
+        <v>32</v>
+      </c>
+      <c r="E25" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F25" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G25" s="4">
         <v>22730</v>
       </c>
-      <c r="H25" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" s="7" t="s">
+      <c r="H25" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I25" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1951,34 +1925,34 @@
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="7">
-        <v>32</v>
-      </c>
-      <c r="E26" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F26" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G26" s="7">
+      <c r="C26" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D26" s="4">
+        <v>32</v>
+      </c>
+      <c r="E26" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G26" s="4">
         <v>22743</v>
       </c>
-      <c r="H26" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I26" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="7" t="s">
+      <c r="H26" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I26" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1986,34 +1960,34 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="7">
-        <v>32</v>
-      </c>
-      <c r="E27" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F27" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G27" s="7">
+      <c r="C27" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="4">
+        <v>32</v>
+      </c>
+      <c r="E27" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G27" s="4">
         <v>22744</v>
       </c>
-      <c r="H27" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I27" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" s="7" t="s">
+      <c r="H27" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I27" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2021,34 +1995,34 @@
       <c r="A28" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D28" s="7">
-        <v>32</v>
-      </c>
-      <c r="E28" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F28" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="C28" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D28" s="4">
+        <v>32</v>
+      </c>
+      <c r="E28" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F28" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G28" s="4">
         <v>22775</v>
       </c>
-      <c r="H28" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I28" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K28" s="7" t="s">
+      <c r="H28" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I28" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2056,34 +2030,34 @@
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D29" s="7">
-        <v>32</v>
-      </c>
-      <c r="E29" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F29" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G29" s="7">
+      <c r="C29" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D29" s="4">
+        <v>32</v>
+      </c>
+      <c r="E29" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F29" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G29" s="4">
         <v>22784</v>
       </c>
-      <c r="H29" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I29" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="7" t="s">
+      <c r="H29" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I29" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2091,34 +2065,34 @@
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D30" s="7">
-        <v>32</v>
-      </c>
-      <c r="E30" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F30" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G30" s="7">
+      <c r="C30" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D30" s="4">
+        <v>32</v>
+      </c>
+      <c r="E30" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F30" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G30" s="4">
         <v>22791</v>
       </c>
-      <c r="H30" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I30" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K30" s="7" t="s">
+      <c r="H30" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I30" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2126,34 +2100,34 @@
       <c r="A31" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D31" s="7">
-        <v>32</v>
-      </c>
-      <c r="E31" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F31" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G31" s="7">
+      <c r="C31" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="4">
+        <v>32</v>
+      </c>
+      <c r="E31" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F31" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G31" s="4">
         <v>22797</v>
       </c>
-      <c r="H31" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I31" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K31" s="7" t="s">
+      <c r="H31" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I31" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2161,34 +2135,34 @@
       <c r="A32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D32" s="7">
-        <v>32</v>
-      </c>
-      <c r="E32" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F32" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G32" s="7">
+      <c r="C32" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D32" s="4">
+        <v>32</v>
+      </c>
+      <c r="E32" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F32" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G32" s="4">
         <v>22799</v>
       </c>
-      <c r="H32" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I32" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="7" t="s">
+      <c r="H32" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I32" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2196,34 +2170,34 @@
       <c r="A33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D33" s="7">
-        <v>32</v>
-      </c>
-      <c r="E33" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F33" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G33" s="7">
+      <c r="C33" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D33" s="4">
+        <v>32</v>
+      </c>
+      <c r="E33" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F33" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G33" s="4">
         <v>22814</v>
       </c>
-      <c r="H33" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I33" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K33" s="7" t="s">
+      <c r="H33" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I33" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2231,34 +2205,34 @@
       <c r="A34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D34" s="7">
-        <v>32</v>
-      </c>
-      <c r="E34" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F34" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G34" s="7">
+      <c r="C34" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D34" s="4">
+        <v>32</v>
+      </c>
+      <c r="E34" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F34" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G34" s="4">
         <v>22815</v>
       </c>
-      <c r="H34" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I34" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K34" s="7" t="s">
+      <c r="H34" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I34" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2266,34 +2240,34 @@
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D35" s="7">
-        <v>32</v>
-      </c>
-      <c r="E35" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F35" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G35" s="7">
+      <c r="C35" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D35" s="4">
+        <v>32</v>
+      </c>
+      <c r="E35" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F35" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G35" s="4">
         <v>22816</v>
       </c>
-      <c r="H35" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I35" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K35" s="7" t="s">
+      <c r="H35" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I35" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2301,34 +2275,34 @@
       <c r="A36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D36" s="7">
-        <v>32</v>
-      </c>
-      <c r="E36" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F36" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G36" s="7">
+      <c r="C36" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D36" s="4">
+        <v>32</v>
+      </c>
+      <c r="E36" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F36" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G36" s="4">
         <v>22821</v>
       </c>
-      <c r="H36" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I36" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K36" s="7" t="s">
+      <c r="H36" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I36" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2336,34 +2310,34 @@
       <c r="A37" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D37" s="7">
-        <v>32</v>
-      </c>
-      <c r="E37" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F37" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G37" s="7">
+      <c r="C37" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D37" s="4">
+        <v>32</v>
+      </c>
+      <c r="E37" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F37" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G37" s="4">
         <v>22824</v>
       </c>
-      <c r="H37" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I37" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K37" s="7" t="s">
+      <c r="H37" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I37" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2371,34 +2345,34 @@
       <c r="A38" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D38" s="7">
-        <v>32</v>
-      </c>
-      <c r="E38" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F38" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G38" s="7">
+      <c r="C38" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D38" s="4">
+        <v>32</v>
+      </c>
+      <c r="E38" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F38" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G38" s="4">
         <v>22835</v>
       </c>
-      <c r="H38" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I38" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K38" s="7" t="s">
+      <c r="H38" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I38" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2406,34 +2380,34 @@
       <c r="A39" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D39" s="7">
-        <v>32</v>
-      </c>
-      <c r="E39" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F39" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G39" s="7">
+      <c r="C39" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D39" s="4">
+        <v>32</v>
+      </c>
+      <c r="E39" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F39" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G39" s="4">
         <v>22836</v>
       </c>
-      <c r="H39" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I39" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K39" s="7" t="s">
+      <c r="H39" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I39" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2441,34 +2415,34 @@
       <c r="A40" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D40" s="7">
-        <v>32</v>
-      </c>
-      <c r="E40" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F40" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G40" s="7">
+      <c r="C40" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D40" s="4">
+        <v>32</v>
+      </c>
+      <c r="E40" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F40" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G40" s="4">
         <v>22844</v>
       </c>
-      <c r="H40" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I40" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K40" s="7" t="s">
+      <c r="H40" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I40" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2476,34 +2450,34 @@
       <c r="A41" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D41" s="7">
-        <v>32</v>
-      </c>
-      <c r="E41" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F41" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G41" s="7">
+      <c r="C41" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D41" s="4">
+        <v>32</v>
+      </c>
+      <c r="E41" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F41" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G41" s="4">
         <v>22847</v>
       </c>
-      <c r="H41" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I41" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K41" s="7" t="s">
+      <c r="H41" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I41" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2511,34 +2485,34 @@
       <c r="A42" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D42" s="7">
-        <v>32</v>
-      </c>
-      <c r="E42" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F42" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G42" s="7">
+      <c r="C42" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D42" s="4">
+        <v>32</v>
+      </c>
+      <c r="E42" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F42" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G42" s="4">
         <v>22852</v>
       </c>
-      <c r="H42" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I42" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K42" s="7" t="s">
+      <c r="H42" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I42" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2546,34 +2520,34 @@
       <c r="A43" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D43" s="7">
-        <v>32</v>
-      </c>
-      <c r="E43" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F43" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G43" s="7">
+      <c r="C43" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D43" s="4">
+        <v>32</v>
+      </c>
+      <c r="E43" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F43" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G43" s="4">
         <v>22863</v>
       </c>
-      <c r="H43" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I43" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K43" s="7" t="s">
+      <c r="H43" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I43" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2581,34 +2555,34 @@
       <c r="A44" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D44" s="7">
-        <v>32</v>
-      </c>
-      <c r="E44" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F44" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G44" s="7">
+      <c r="C44" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D44" s="4">
+        <v>32</v>
+      </c>
+      <c r="E44" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F44" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G44" s="4">
         <v>22866</v>
       </c>
-      <c r="H44" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I44" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K44" s="7" t="s">
+      <c r="H44" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I44" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K44" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2616,34 +2590,34 @@
       <c r="A45" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D45" s="7">
-        <v>32</v>
-      </c>
-      <c r="E45" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F45" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G45" s="7">
+      <c r="C45" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D45" s="4">
+        <v>32</v>
+      </c>
+      <c r="E45" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F45" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G45" s="4">
         <v>22867</v>
       </c>
-      <c r="H45" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I45" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K45" s="7" t="s">
+      <c r="H45" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I45" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2651,34 +2625,34 @@
       <c r="A46" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D46" s="7">
-        <v>32</v>
-      </c>
-      <c r="E46" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F46" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G46" s="7">
+      <c r="C46" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D46" s="4">
+        <v>32</v>
+      </c>
+      <c r="E46" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F46" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G46" s="4">
         <v>22898</v>
       </c>
-      <c r="H46" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I46" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K46" s="7" t="s">
+      <c r="H46" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I46" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2686,34 +2660,34 @@
       <c r="A47" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D47" s="7">
-        <v>32</v>
-      </c>
-      <c r="E47" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F47" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G47" s="7">
+      <c r="C47" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D47" s="4">
+        <v>32</v>
+      </c>
+      <c r="E47" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G47" s="4">
         <v>22899</v>
       </c>
-      <c r="H47" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I47" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K47" s="7" t="s">
+      <c r="H47" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I47" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K47" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2721,34 +2695,34 @@
       <c r="A48" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D48" s="7">
-        <v>32</v>
-      </c>
-      <c r="E48" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F48" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G48" s="7">
+      <c r="C48" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D48" s="4">
+        <v>32</v>
+      </c>
+      <c r="E48" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F48" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G48" s="4">
         <v>22904</v>
       </c>
-      <c r="H48" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I48" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K48" s="7" t="s">
+      <c r="H48" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I48" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2756,34 +2730,34 @@
       <c r="A49" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C49" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D49" s="7">
-        <v>32</v>
-      </c>
-      <c r="E49" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F49" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G49" s="7">
+      <c r="C49" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D49" s="4">
+        <v>32</v>
+      </c>
+      <c r="E49" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F49" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G49" s="4">
         <v>22905</v>
       </c>
-      <c r="H49" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I49" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K49" s="7" t="s">
+      <c r="H49" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I49" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2791,34 +2765,34 @@
       <c r="A50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D50" s="7">
-        <v>32</v>
-      </c>
-      <c r="E50" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F50" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G50" s="7">
+      <c r="C50" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D50" s="4">
+        <v>32</v>
+      </c>
+      <c r="E50" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F50" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G50" s="4">
         <v>22922</v>
       </c>
-      <c r="H50" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I50" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K50" s="7" t="s">
+      <c r="H50" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I50" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K50" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2826,34 +2800,34 @@
       <c r="A51" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D51" s="7">
-        <v>32</v>
-      </c>
-      <c r="E51" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F51" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G51" s="7">
+      <c r="C51" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D51" s="4">
+        <v>32</v>
+      </c>
+      <c r="E51" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F51" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G51" s="4">
         <v>22948</v>
       </c>
-      <c r="H51" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I51" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K51" s="7" t="s">
+      <c r="H51" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I51" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K51" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2861,34 +2835,34 @@
       <c r="A52" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D52" s="7">
-        <v>32</v>
-      </c>
-      <c r="E52" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F52" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G52" s="7">
+      <c r="C52" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D52" s="4">
+        <v>32</v>
+      </c>
+      <c r="E52" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F52" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G52" s="4">
         <v>22677</v>
       </c>
-      <c r="H52" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I52" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K52" s="7" t="s">
+      <c r="H52" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I52" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K52" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2896,34 +2870,34 @@
       <c r="A53" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D53" s="7">
-        <v>32</v>
-      </c>
-      <c r="E53" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F53" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G53" s="7">
+      <c r="C53" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D53" s="4">
+        <v>32</v>
+      </c>
+      <c r="E53" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F53" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G53" s="4">
         <v>21381</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="7">
         <v>46204</v>
       </c>
-      <c r="I53" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K53" s="7" t="s">
+      <c r="I53" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2931,34 +2905,34 @@
       <c r="A54" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D54" s="7">
-        <v>32</v>
-      </c>
-      <c r="E54" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F54" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G54" s="7">
+      <c r="C54" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D54" s="4">
+        <v>32</v>
+      </c>
+      <c r="E54" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F54" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G54" s="4">
         <v>22112</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="7">
         <v>46204</v>
       </c>
-      <c r="I54" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K54" s="7" t="s">
+      <c r="I54" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2966,34 +2940,34 @@
       <c r="A55" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C55" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D55" s="7">
-        <v>32</v>
-      </c>
-      <c r="E55" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F55" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G55" s="7">
+      <c r="C55" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D55" s="4">
+        <v>32</v>
+      </c>
+      <c r="E55" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F55" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G55" s="4">
         <v>21202</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="7">
         <v>46204</v>
       </c>
-      <c r="I55" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K55" s="7" t="s">
+      <c r="I55" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K55" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3001,34 +2975,34 @@
       <c r="A56" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D56" s="7">
-        <v>32</v>
-      </c>
-      <c r="E56" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F56" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G56" s="7">
+      <c r="C56" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D56" s="4">
+        <v>32</v>
+      </c>
+      <c r="E56" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F56" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G56" s="4">
         <v>21488</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H56" s="7">
         <v>46204</v>
       </c>
-      <c r="I56" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K56" s="7" t="s">
+      <c r="I56" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K56" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3036,34 +3010,34 @@
       <c r="A57" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D57" s="7">
-        <v>32</v>
-      </c>
-      <c r="E57" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F57" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G57" s="7">
+      <c r="C57" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D57" s="4">
+        <v>32</v>
+      </c>
+      <c r="E57" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F57" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G57" s="4">
         <v>21608</v>
       </c>
-      <c r="H57" s="10">
+      <c r="H57" s="7">
         <v>46204</v>
       </c>
-      <c r="I57" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K57" s="7" t="s">
+      <c r="I57" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K57" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3071,34 +3045,34 @@
       <c r="A58" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D58" s="7">
-        <v>32</v>
-      </c>
-      <c r="E58" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F58" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G58" s="7">
+      <c r="C58" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D58" s="4">
+        <v>32</v>
+      </c>
+      <c r="E58" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F58" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G58" s="4">
         <v>22945</v>
       </c>
-      <c r="H58" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I58" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K58" s="7" t="s">
+      <c r="H58" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I58" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K58" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3106,34 +3080,34 @@
       <c r="A59" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C59" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D59" s="7">
-        <v>32</v>
-      </c>
-      <c r="E59" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F59" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G59" s="7">
+      <c r="C59" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D59" s="4">
+        <v>32</v>
+      </c>
+      <c r="E59" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F59" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G59" s="4">
         <v>22362</v>
       </c>
-      <c r="H59" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I59" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K59" s="7" t="s">
+      <c r="H59" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I59" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K59" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3141,34 +3115,34 @@
       <c r="A60" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D60" s="7">
-        <v>32</v>
-      </c>
-      <c r="E60" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F60" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G60" s="7">
+      <c r="C60" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D60" s="4">
+        <v>32</v>
+      </c>
+      <c r="E60" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F60" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G60" s="4">
         <v>22729</v>
       </c>
-      <c r="H60" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I60" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K60" s="7" t="s">
+      <c r="H60" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I60" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3176,53 +3150,56 @@
       <c r="A61" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C61" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D61" s="7">
-        <v>32</v>
-      </c>
-      <c r="E61" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F61" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G61" s="7">
+      <c r="C61" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D61" s="4">
+        <v>32</v>
+      </c>
+      <c r="E61" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F61" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G61" s="4">
         <v>22817</v>
       </c>
-      <c r="H61" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I61" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K61" s="7" t="s">
+      <c r="H61" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I61" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="K62" s="12"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F63" s="5"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F64" s="5"/>
-    </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F65" s="5"/>
-    </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F66" s="5"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="3"/>
+    </row>
+    <row r="65" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E65" s="6"/>
+      <c r="F65" s="3"/>
+    </row>
+    <row r="66" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E66" s="6"/>
+      <c r="F66" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K61" xr:uid="{E8A0EE67-8DF1-4794-B2EE-C34392B23DA5}">
@@ -3285,388 +3262,388 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="7">
-        <v>32</v>
-      </c>
-      <c r="E2" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F2" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="C2" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="4">
+        <v>32</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G2" s="4">
         <v>22132</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="7">
         <v>46204</v>
       </c>
-      <c r="I2" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="I2" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="7">
-        <v>32</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F3" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="C3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="4">
+        <v>32</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G3" s="4">
         <v>22885</v>
       </c>
-      <c r="H3" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I3" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="H3" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I3" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="7">
-        <v>32</v>
-      </c>
-      <c r="E4" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F4" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="C4" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="4">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G4" s="4">
         <v>22896</v>
       </c>
-      <c r="H4" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I4" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="H4" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="7">
-        <v>32</v>
-      </c>
-      <c r="E5" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F5" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="C5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="4">
+        <v>32</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G5" s="4">
         <v>22930</v>
       </c>
-      <c r="H5" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I5" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="H5" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I5" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="7">
-        <v>32</v>
-      </c>
-      <c r="E6" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F6" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="C6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="4">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G6" s="4">
         <v>22944</v>
       </c>
-      <c r="H6" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I6" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="H6" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I6" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="7">
-        <v>32</v>
-      </c>
-      <c r="E7" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F7" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="C7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="4">
+        <v>32</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G7" s="4">
         <v>22573</v>
       </c>
-      <c r="H7" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I7" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="H7" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I7" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="7">
-        <v>32</v>
-      </c>
-      <c r="E8" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F8" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="C8" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="4">
+        <v>32</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G8" s="4">
         <v>22149</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="7">
         <v>46204</v>
       </c>
-      <c r="I8" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="I8" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="7">
-        <v>32</v>
-      </c>
-      <c r="E9" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F9" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G9" s="7">
+      <c r="C9" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="4">
+        <v>32</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G9" s="4">
         <v>22619</v>
       </c>
-      <c r="H9" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I9" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="7" t="s">
+      <c r="H9" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="7">
-        <v>32</v>
-      </c>
-      <c r="E10" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F10" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="C10" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32</v>
+      </c>
+      <c r="E10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G10" s="4">
         <v>22908</v>
       </c>
-      <c r="H10" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I10" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="7" t="s">
+      <c r="H10" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="7">
-        <v>32</v>
-      </c>
-      <c r="E11" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F11" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="C11" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="4">
+        <v>32</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G11" s="4">
         <v>21551</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="7">
         <v>46204</v>
       </c>
-      <c r="I11" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="7" t="s">
+      <c r="I11" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="7">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="7">
-        <v>32</v>
-      </c>
-      <c r="E12" s="9">
-        <v>46251</v>
-      </c>
-      <c r="F12" s="9">
-        <v>46255</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="C12" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="4">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G12" s="4">
         <v>22659</v>
       </c>
-      <c r="H12" s="10">
-        <v>46235</v>
-      </c>
-      <c r="I12" s="9">
-        <v>46251</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="H12" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>33</v>
       </c>
     </row>

--- a/data/base/Backlog_32.xlsx
+++ b/data/base/Backlog_32.xlsx
@@ -8,24 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C27970-AFB9-4025-9ABB-14B24DD04E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66143109-2D1F-41CA-9E4D-4BC732324330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7B6DCF3-E10E-448D-89E5-FD6D35B80F1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F7B6DCF3-E10E-448D-89E5-FD6D35B80F1D}"/>
   </bookViews>
   <sheets>
-    <sheet name="ITI" sheetId="1" r:id="rId1"/>
-    <sheet name="SPN" sheetId="2" r:id="rId2"/>
+    <sheet name="SPN" sheetId="2" r:id="rId1"/>
+    <sheet name="ITI" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="33">
   <si>
     <t>Status</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>ITI</t>
-  </si>
-  <si>
-    <t>Pentende</t>
   </si>
   <si>
     <t>SPN</t>
@@ -1029,6 +1026,512 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBC2873-7AB6-4A6F-B446-6C8FD02AA69D}">
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="4">
+        <v>32</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G2" s="4">
+        <v>22132</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46204</v>
+      </c>
+      <c r="I2" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="4">
+        <v>32</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G3" s="4">
+        <v>22885</v>
+      </c>
+      <c r="H3" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I3" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="4">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G4" s="4">
+        <v>22896</v>
+      </c>
+      <c r="H4" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="4">
+        <v>32</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G5" s="4">
+        <v>22930</v>
+      </c>
+      <c r="H5" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I5" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="4">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G6" s="4">
+        <v>22944</v>
+      </c>
+      <c r="H6" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I6" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="4">
+        <v>32</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G7" s="4">
+        <v>22573</v>
+      </c>
+      <c r="H7" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I7" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="4">
+        <v>32</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G8" s="4">
+        <v>22149</v>
+      </c>
+      <c r="H8" s="7">
+        <v>46204</v>
+      </c>
+      <c r="I8" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="4">
+        <v>32</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G9" s="4">
+        <v>22619</v>
+      </c>
+      <c r="H9" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32</v>
+      </c>
+      <c r="E10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G10" s="4">
+        <v>22908</v>
+      </c>
+      <c r="H10" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="4">
+        <v>32</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G11" s="4">
+        <v>21551</v>
+      </c>
+      <c r="H11" s="7">
+        <v>46204</v>
+      </c>
+      <c r="I11" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="4">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46255</v>
+      </c>
+      <c r="G12" s="4">
+        <v>22659</v>
+      </c>
+      <c r="H12" s="7">
+        <v>46235</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46251</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{BBBC2873-7AB6-4A6F-B446-6C8FD02AA69D}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K13">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8A0EE67-8DF1-4794-B2EE-C34392B23DA5}">
   <dimension ref="A1:K66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1110,7 +1613,7 @@
         <v>46251</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>14</v>
@@ -1145,7 +1648,7 @@
         <v>46251</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>14</v>
@@ -1180,7 +1683,7 @@
         <v>46251</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>14</v>
@@ -1215,7 +1718,7 @@
         <v>46251</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>14</v>
@@ -1250,7 +1753,7 @@
         <v>46251</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>14</v>
@@ -1285,7 +1788,7 @@
         <v>46251</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>14</v>
@@ -1320,7 +1823,7 @@
         <v>46251</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>14</v>
@@ -1355,7 +1858,7 @@
         <v>46251</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>14</v>
@@ -1390,7 +1893,7 @@
         <v>46251</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>14</v>
@@ -1425,7 +1928,7 @@
         <v>46251</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>14</v>
@@ -1460,7 +1963,7 @@
         <v>46251</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>14</v>
@@ -1495,7 +1998,7 @@
         <v>46251</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>14</v>
@@ -1530,7 +2033,7 @@
         <v>46251</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>14</v>
@@ -1565,7 +2068,7 @@
         <v>46251</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>14</v>
@@ -1600,7 +2103,7 @@
         <v>46251</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>14</v>
@@ -1635,7 +2138,7 @@
         <v>46251</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>14</v>
@@ -1670,7 +2173,7 @@
         <v>46251</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>14</v>
@@ -1705,7 +2208,7 @@
         <v>46251</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>14</v>
@@ -1740,7 +2243,7 @@
         <v>46251</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>14</v>
@@ -1775,7 +2278,7 @@
         <v>46251</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>14</v>
@@ -1810,7 +2313,7 @@
         <v>46251</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>14</v>
@@ -1845,7 +2348,7 @@
         <v>46251</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>14</v>
@@ -1880,7 +2383,7 @@
         <v>46251</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>14</v>
@@ -1915,7 +2418,7 @@
         <v>46251</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>14</v>
@@ -1950,7 +2453,7 @@
         <v>46251</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>14</v>
@@ -1985,7 +2488,7 @@
         <v>46251</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>14</v>
@@ -2020,7 +2523,7 @@
         <v>46251</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>14</v>
@@ -2055,7 +2558,7 @@
         <v>46251</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>14</v>
@@ -2090,7 +2593,7 @@
         <v>46251</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>14</v>
@@ -2125,7 +2628,7 @@
         <v>46251</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>14</v>
@@ -2160,7 +2663,7 @@
         <v>46251</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>14</v>
@@ -2195,7 +2698,7 @@
         <v>46251</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>14</v>
@@ -2230,7 +2733,7 @@
         <v>46251</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>14</v>
@@ -2265,7 +2768,7 @@
         <v>46251</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>14</v>
@@ -2300,7 +2803,7 @@
         <v>46251</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>14</v>
@@ -2335,7 +2838,7 @@
         <v>46251</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>14</v>
@@ -2370,7 +2873,7 @@
         <v>46251</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>14</v>
@@ -2405,7 +2908,7 @@
         <v>46251</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>14</v>
@@ -2440,7 +2943,7 @@
         <v>46251</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>14</v>
@@ -2475,7 +2978,7 @@
         <v>46251</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>14</v>
@@ -2510,7 +3013,7 @@
         <v>46251</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>14</v>
@@ -2545,7 +3048,7 @@
         <v>46251</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>14</v>
@@ -2580,7 +3083,7 @@
         <v>46251</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>14</v>
@@ -2615,7 +3118,7 @@
         <v>46251</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>14</v>
@@ -2650,7 +3153,7 @@
         <v>46251</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>14</v>
@@ -2685,7 +3188,7 @@
         <v>46251</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>14</v>
@@ -2720,7 +3223,7 @@
         <v>46251</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>14</v>
@@ -2755,7 +3258,7 @@
         <v>46251</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>14</v>
@@ -2790,7 +3293,7 @@
         <v>46251</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>14</v>
@@ -2825,7 +3328,7 @@
         <v>46251</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>14</v>
@@ -2860,7 +3363,7 @@
         <v>46251</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>14</v>
@@ -2895,7 +3398,7 @@
         <v>46251</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>14</v>
@@ -2930,7 +3433,7 @@
         <v>46251</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>14</v>
@@ -2965,7 +3468,7 @@
         <v>46251</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>14</v>
@@ -3000,7 +3503,7 @@
         <v>46251</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>14</v>
@@ -3035,7 +3538,7 @@
         <v>46251</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>14</v>
@@ -3070,7 +3573,7 @@
         <v>46251</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>14</v>
@@ -3105,7 +3608,7 @@
         <v>46251</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>14</v>
@@ -3140,7 +3643,7 @@
         <v>46251</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>14</v>
@@ -3175,7 +3678,7 @@
         <v>46251</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>14</v>
@@ -3209,510 +3712,4 @@
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBC2873-7AB6-4A6F-B446-6C8FD02AA69D}">
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="4">
-        <v>32</v>
-      </c>
-      <c r="E2" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G2" s="4">
-        <v>22132</v>
-      </c>
-      <c r="H2" s="7">
-        <v>46204</v>
-      </c>
-      <c r="I2" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="4">
-        <v>32</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G3" s="4">
-        <v>22885</v>
-      </c>
-      <c r="H3" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I3" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="4">
-        <v>32</v>
-      </c>
-      <c r="E4" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G4" s="4">
-        <v>22896</v>
-      </c>
-      <c r="H4" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I4" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="4">
-        <v>32</v>
-      </c>
-      <c r="E5" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G5" s="4">
-        <v>22930</v>
-      </c>
-      <c r="H5" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I5" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="4">
-        <v>32</v>
-      </c>
-      <c r="E6" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G6" s="4">
-        <v>22944</v>
-      </c>
-      <c r="H6" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I6" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="4">
-        <v>32</v>
-      </c>
-      <c r="E7" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G7" s="4">
-        <v>22573</v>
-      </c>
-      <c r="H7" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I7" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="4">
-        <v>32</v>
-      </c>
-      <c r="E8" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G8" s="4">
-        <v>22149</v>
-      </c>
-      <c r="H8" s="7">
-        <v>46204</v>
-      </c>
-      <c r="I8" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="4">
-        <v>32</v>
-      </c>
-      <c r="E9" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G9" s="4">
-        <v>22619</v>
-      </c>
-      <c r="H9" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I9" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="4">
-        <v>32</v>
-      </c>
-      <c r="E10" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G10" s="4">
-        <v>22908</v>
-      </c>
-      <c r="H10" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I10" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="4">
-        <v>32</v>
-      </c>
-      <c r="E11" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G11" s="4">
-        <v>21551</v>
-      </c>
-      <c r="H11" s="7">
-        <v>46204</v>
-      </c>
-      <c r="I11" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="4">
-        <v>32</v>
-      </c>
-      <c r="E12" s="6">
-        <v>46251</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46255</v>
-      </c>
-      <c r="G12" s="4">
-        <v>22659</v>
-      </c>
-      <c r="H12" s="7">
-        <v>46235</v>
-      </c>
-      <c r="I12" s="6">
-        <v>46251</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{BBBC2873-7AB6-4A6F-B446-6C8FD02AA69D}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K13">
-      <sortCondition ref="B1"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>